--- a/data/trans_dic/P11_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,01</t>
+          <t>4,6; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,31</t>
+          <t>3,92; 8,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,81</t>
+          <t>2,63; 7,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,58</t>
+          <t>3,59; 13,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,06</t>
+          <t>5,12; 9,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,07</t>
+          <t>6,56; 11,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,02</t>
+          <t>4,21; 9,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,41</t>
+          <t>6,81; 16,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,43</t>
+          <t>5,29; 8,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,97</t>
+          <t>5,75; 9,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,12</t>
+          <t>3,73; 6,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,88</t>
+          <t>5,73; 12,46</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,73</t>
+          <t>4,07; 7,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,92</t>
+          <t>6,0; 10,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,27; 20,01</t>
+          <t>11,77; 20,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 17,08</t>
+          <t>11,47; 17,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,4</t>
+          <t>6,75; 11,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,27</t>
+          <t>8,33; 13,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,37</t>
+          <t>8,5; 18,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,25</t>
+          <t>7,97; 11,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 10,44</t>
+          <t>7,05; 10,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,47</t>
+          <t>7,93; 11,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 17,73</t>
+          <t>11,22; 18,04</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,11</t>
+          <t>8,47; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,44</t>
+          <t>10,06; 14,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,45</t>
+          <t>8,96; 13,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,44</t>
+          <t>15,67; 22,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,45; 23,73</t>
+          <t>17,58; 23,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 22,31</t>
+          <t>16,0; 22,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,72</t>
+          <t>12,06; 17,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,18</t>
+          <t>20,31; 26,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 17,84</t>
+          <t>13,77; 17,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 17,91</t>
+          <t>13,65; 17,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,17</t>
+          <t>11,15; 14,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,47</t>
+          <t>18,71; 23,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 21,94</t>
+          <t>14,92; 21,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,47</t>
+          <t>11,47; 17,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 22,05</t>
+          <t>15,7; 22,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 27,86</t>
+          <t>8,45; 27,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 33,96</t>
+          <t>26,17; 33,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,28; 30,7</t>
+          <t>23,23; 30,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 27,16</t>
+          <t>20,41; 27,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 37,38</t>
+          <t>27,88; 36,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 26,75</t>
+          <t>21,63; 26,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,09</t>
+          <t>18,31; 23,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 23,55</t>
+          <t>18,93; 23,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 31,33</t>
+          <t>16,43; 31,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,07; 35,52</t>
+          <t>26,6; 35,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 31,35</t>
+          <t>22,43; 31,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 29,06</t>
+          <t>20,76; 28,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,72; 42,97</t>
+          <t>35,34; 43,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,76; 43,34</t>
+          <t>33,7; 43,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,89; 50,96</t>
+          <t>41,16; 51,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,36; 45,88</t>
+          <t>36,65; 46,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,72; 48,96</t>
+          <t>42,78; 49,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,39; 38,2</t>
+          <t>31,47; 38,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 40,09</t>
+          <t>33,25; 40,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,33; 36,52</t>
+          <t>30,03; 36,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,02; 45,1</t>
+          <t>40,35; 45,29</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,52; 43,41</t>
+          <t>32,6; 43,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,16; 46,14</t>
+          <t>34,75; 47,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,14; 37,34</t>
+          <t>27,33; 38,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,77; 39,76</t>
+          <t>31,87; 39,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,51; 59,77</t>
+          <t>49,72; 59,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,8; 64,66</t>
+          <t>54,43; 64,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,09; 59,32</t>
+          <t>48,63; 59,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,29; 86,93</t>
+          <t>50,57; 87,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,06; 50,87</t>
+          <t>43,09; 51,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,24; 54,35</t>
+          <t>46,52; 54,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,65; 47,5</t>
+          <t>40,35; 47,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,2; 79,03</t>
+          <t>43,21; 77,78</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54,17; 67,03</t>
+          <t>54,22; 67,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,05; 67,47</t>
+          <t>53,5; 67,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,39; 59,68</t>
+          <t>48,98; 59,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,82; 56,0</t>
+          <t>46,56; 56,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,12; 73,17</t>
+          <t>62,49; 73,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,72; 81,83</t>
+          <t>72,85; 81,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,58; 74,54</t>
+          <t>63,91; 74,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,79; 81,31</t>
+          <t>75,71; 81,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,19; 69,51</t>
+          <t>60,85; 69,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67,42; 75,07</t>
+          <t>67,23; 74,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,34; 67,23</t>
+          <t>59,35; 67,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,18; 70,46</t>
+          <t>64,99; 70,32</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,88; 19,62</t>
+          <t>16,92; 19,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,28</t>
+          <t>17,54; 20,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,35; 19,91</t>
+          <t>17,31; 20,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,57; 27,47</t>
+          <t>19,41; 27,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,56; 30,67</t>
+          <t>27,64; 30,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,12</t>
+          <t>29,8; 33,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,35; 30,48</t>
+          <t>27,23; 30,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,8; 50,77</t>
+          <t>35,95; 51,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,87</t>
+          <t>22,7; 24,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,18; 26,34</t>
+          <t>24,14; 26,26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,91</t>
+          <t>22,87; 24,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,64; 40,15</t>
+          <t>29,65; 38,99</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22561; 44500</t>
+          <t>22738; 45130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17218; 37499</t>
+          <t>17681; 38283</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10344; 28256</t>
+          <t>10926; 29100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13792; 50331</t>
+          <t>14364; 54584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23066; 47024</t>
+          <t>23948; 44607</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28264; 51947</t>
+          <t>28232; 51399</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16557; 35700</t>
+          <t>16660; 35826</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22058; 54542</t>
+          <t>21319; 53085</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50590; 81042</t>
+          <t>50863; 82410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49795; 79114</t>
+          <t>50661; 80764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30706; 57693</t>
+          <t>30210; 55818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42792; 91891</t>
+          <t>40830; 88874</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30896; 56827</t>
+          <t>29907; 56657</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43797; 73879</t>
+          <t>43774; 73920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35872; 63850</t>
+          <t>35083; 63809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47747; 84741</t>
+          <t>49840; 87168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70374; 106821</t>
+          <t>71758; 106787</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39685; 69435</t>
+          <t>41106; 69894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46144; 74438</t>
+          <t>46688; 75673</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43255; 93968</t>
+          <t>43460; 93531</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108386; 153084</t>
+          <t>108517; 153342</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92164; 134753</t>
+          <t>91062; 132876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89727; 131300</t>
+          <t>90842; 130246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>100221; 165759</t>
+          <t>104928; 168693</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53719; 83713</t>
+          <t>54086; 85254</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67049; 104823</t>
+          <t>68332; 101548</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60544; 95965</t>
+          <t>59493; 92674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82284; 120353</t>
+          <t>84024; 121307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>120330; 163659</t>
+          <t>121228; 165281</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>115331; 157968</t>
+          <t>113268; 156504</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78530; 115880</t>
+          <t>78860; 114379</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>110717; 141997</t>
+          <t>110176; 142135</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184339; 237002</t>
+          <t>182952; 237947</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>192996; 248392</t>
+          <t>189326; 244282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149917; 199921</t>
+          <t>146940; 195451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>203044; 253188</t>
+          <t>201834; 248184</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76910; 113909</t>
+          <t>77449; 112981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70479; 107181</t>
+          <t>70371; 107476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98741; 141584</t>
+          <t>100837; 142360</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75013; 247301</t>
+          <t>75003; 248306</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>133846; 175092</t>
+          <t>134951; 175176</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143462; 189185</t>
+          <t>143133; 189428</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>128249; 175512</t>
+          <t>131887; 175885</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199972; 266454</t>
+          <t>198776; 263356</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222468; 276789</t>
+          <t>223854; 278898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>223335; 284001</t>
+          <t>225191; 284036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>242295; 303436</t>
+          <t>243847; 306077</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>244050; 501471</t>
+          <t>263019; 503249</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100822; 137341</t>
+          <t>102858; 137575</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95979; 134020</t>
+          <t>95900; 133560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98721; 137947</t>
+          <t>98534; 137602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199663; 240156</t>
+          <t>197532; 242652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136372; 175106</t>
+          <t>136156; 175821</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>183111; 228207</t>
+          <t>184324; 230267</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>179418; 226386</t>
+          <t>180865; 228264</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>234064; 268261</t>
+          <t>234382; 269539</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>248201; 302059</t>
+          <t>248842; 302655</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>290947; 350871</t>
+          <t>291049; 352237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>293607; 353507</t>
+          <t>290760; 352430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>442936; 499150</t>
+          <t>446595; 501309</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>95134; 127003</t>
+          <t>95376; 126398</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>105481; 142468</t>
+          <t>107292; 145413</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90464; 124443</t>
+          <t>91089; 126771</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>116970; 146398</t>
+          <t>117336; 146411</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>169804; 204955</t>
+          <t>170520; 203910</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>190432; 228883</t>
+          <t>192694; 228447</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>184941; 223476</t>
+          <t>183195; 223950</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>305343; 527842</t>
+          <t>307052; 533637</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>273679; 323268</t>
+          <t>273853; 324179</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>306467; 360215</t>
+          <t>308295; 358359</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>281512; 337223</t>
+          <t>286461; 337406</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>421331; 770885</t>
+          <t>421506; 758663</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113694; 140689</t>
+          <t>113808; 141850</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>133898; 167141</t>
+          <t>132545; 166872</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123972; 152899</t>
+          <t>125484; 153587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132038; 157946</t>
+          <t>131315; 158817</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>207440; 244306</t>
+          <t>208675; 245194</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>282851; 318294</t>
+          <t>283356; 317518</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>251250; 294559</t>
+          <t>252548; 293853</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>320682; 344029</t>
+          <t>320313; 343154</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>332766; 378006</t>
+          <t>330898; 376484</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>429240; 478003</t>
+          <t>428077; 475902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>386523; 437896</t>
+          <t>386618; 438320</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>459629; 496860</t>
+          <t>458230; 495856</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>552983; 642865</t>
+          <t>554337; 643076</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>596618; 691523</t>
+          <t>597889; 692568</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>584514; 670850</t>
+          <t>583392; 675663</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>676549; 949686</t>
+          <t>670918; 946553</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>931344; 1036340</t>
+          <t>933971; 1042379</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1056150; 1177238</t>
+          <t>1059235; 1173836</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>963266; 1073617</t>
+          <t>959073; 1071321</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1309506; 1857299</t>
+          <t>1314973; 1891058</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1514374; 1655188</t>
+          <t>1510899; 1649700</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1684174; 1834398</t>
+          <t>1681452; 1828983</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1567702; 1716472</t>
+          <t>1576319; 1720911</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2109118; 2856413</t>
+          <t>2109545; 2774079</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P11_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,13</t>
+          <t>4,34; 9,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,48</t>
+          <t>3,91; 8,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,02</t>
+          <t>2,54; 7,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,65</t>
+          <t>4,71; 12,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,54</t>
+          <t>4,87; 9,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,95</t>
+          <t>6,49; 12,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,05</t>
+          <t>4,08; 8,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 16,95</t>
+          <t>7,62; 17,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,57</t>
+          <t>5,4; 8,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,16</t>
+          <t>5,76; 9,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,89</t>
+          <t>3,85; 7,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,46</t>
+          <t>7,19; 13,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,7</t>
+          <t>4,18; 7,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,84</t>
+          <t>6,18; 10,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,92</t>
+          <t>6,22; 10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 20,58</t>
+          <t>11,6; 20,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,07</t>
+          <t>11,44; 17,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,47</t>
+          <t>6,82; 11,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,5</t>
+          <t>8,51; 13,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 18,29</t>
+          <t>12,22; 18,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,27</t>
+          <t>7,96; 11,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,29</t>
+          <t>7,22; 10,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,37</t>
+          <t>7,96; 11,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 18,04</t>
+          <t>13,05; 18,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,35</t>
+          <t>8,62; 13,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 14,96</t>
+          <t>10,02; 15,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,95</t>
+          <t>8,94; 14,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,67; 22,62</t>
+          <t>15,3; 22,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 23,96</t>
+          <t>17,56; 23,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 22,11</t>
+          <t>16,0; 22,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,49</t>
+          <t>12,2; 17,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,31; 26,2</t>
+          <t>20,27; 26,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,91</t>
+          <t>13,83; 17,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 17,61</t>
+          <t>13,91; 17,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,83</t>
+          <t>11,28; 14,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,01</t>
+          <t>18,62; 22,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,92; 21,76</t>
+          <t>15,04; 21,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,51</t>
+          <t>11,33; 17,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 22,17</t>
+          <t>15,88; 22,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 27,97</t>
+          <t>22,98; 29,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,17; 33,97</t>
+          <t>25,7; 33,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 30,74</t>
+          <t>23,45; 31,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 27,22</t>
+          <t>20,21; 26,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,88; 36,94</t>
+          <t>31,88; 37,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,63; 26,95</t>
+          <t>21,61; 26,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 23,09</t>
+          <t>17,88; 22,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 23,76</t>
+          <t>18,88; 23,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 31,44</t>
+          <t>28,35; 32,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 35,58</t>
+          <t>26,36; 35,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,43; 31,24</t>
+          <t>22,75; 31,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,76; 28,99</t>
+          <t>20,98; 28,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,34; 43,42</t>
+          <t>33,74; 41,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,7; 43,52</t>
+          <t>33,46; 43,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,16; 51,42</t>
+          <t>41,5; 51,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,65; 46,26</t>
+          <t>36,71; 45,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,78; 49,19</t>
+          <t>42,63; 48,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,47; 38,28</t>
+          <t>31,62; 38,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 40,24</t>
+          <t>33,41; 40,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 36,4</t>
+          <t>30,18; 36,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,35; 45,29</t>
+          <t>39,5; 44,17</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,6; 43,2</t>
+          <t>32,24; 43,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,75; 47,09</t>
+          <t>34,04; 46,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,33; 38,04</t>
+          <t>27,13; 37,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 39,77</t>
+          <t>30,87; 38,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,72; 59,46</t>
+          <t>49,43; 59,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,43; 64,53</t>
+          <t>54,17; 64,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,63; 59,45</t>
+          <t>48,73; 59,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,57; 87,88</t>
+          <t>48,52; 55,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,09; 51,01</t>
+          <t>43,28; 50,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,52; 54,07</t>
+          <t>46,59; 54,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,35; 47,52</t>
+          <t>40,19; 47,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,21; 77,78</t>
+          <t>41,24; 46,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54,22; 67,59</t>
+          <t>54,29; 66,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,5; 67,36</t>
+          <t>53,87; 67,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,98; 59,94</t>
+          <t>48,54; 59,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,56; 56,31</t>
+          <t>46,42; 55,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,49; 73,43</t>
+          <t>62,62; 73,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,85; 81,63</t>
+          <t>73,33; 82,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,91; 74,36</t>
+          <t>63,23; 74,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,71; 81,11</t>
+          <t>75,08; 80,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,85; 69,23</t>
+          <t>60,91; 69,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67,23; 74,74</t>
+          <t>67,64; 74,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,35; 67,29</t>
+          <t>59,43; 67,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,99; 70,32</t>
+          <t>64,41; 69,52</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,63</t>
+          <t>16,88; 19,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,54; 20,31</t>
+          <t>17,52; 20,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,31; 20,05</t>
+          <t>17,39; 20,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,41; 27,38</t>
+          <t>24,8; 27,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,64; 30,85</t>
+          <t>27,78; 30,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 33,02</t>
+          <t>29,68; 32,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,23; 30,42</t>
+          <t>27,19; 30,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,95; 51,69</t>
+          <t>35,69; 38,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,79</t>
+          <t>22,66; 24,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,14; 26,26</t>
+          <t>24,22; 26,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22,87; 24,97</t>
+          <t>22,78; 24,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,65; 38,99</t>
+          <t>30,92; 33,08</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>33494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>76908</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22738; 45130</t>
+          <t>21431; 45368</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17681; 38283</t>
+          <t>17650; 37050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10926; 29100</t>
+          <t>10551; 29077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14364; 54584</t>
+          <t>19221; 52600</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23948; 44607</t>
+          <t>22759; 44365</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28232; 51399</t>
+          <t>27911; 51801</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16660; 35826</t>
+          <t>16129; 34499</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21319; 53085</t>
+          <t>27639; 63675</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50863; 82410</t>
+          <t>51906; 83473</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50661; 80764</t>
+          <t>50775; 79521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30210; 55818</t>
+          <t>31183; 57902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40830; 88874</t>
+          <t>55391; 104327</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>74466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>137489</t>
+          <t>151852</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29907; 56657</t>
+          <t>30768; 57757</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43774; 73920</t>
+          <t>42166; 74506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35083; 63809</t>
+          <t>36376; 62940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49840; 87168</t>
+          <t>55304; 95770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71758; 106787</t>
+          <t>71561; 107084</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41106; 69894</t>
+          <t>41549; 70818</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46688; 75673</t>
+          <t>47703; 75871</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43460; 93531</t>
+          <t>61227; 94821</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108517; 153342</t>
+          <t>108289; 155123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91062; 132876</t>
+          <t>93172; 135383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90842; 130246</t>
+          <t>91182; 129480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104928; 168693</t>
+          <t>127593; 177913</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>124860</t>
+          <t>142051</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>225506</t>
+          <t>255884</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54086; 85254</t>
+          <t>55030; 85127</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68332; 101548</t>
+          <t>68030; 104490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59493; 92674</t>
+          <t>59350; 94044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84024; 121307</t>
+          <t>94966; 136641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>121228; 165281</t>
+          <t>121148; 161906</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>113268; 156504</t>
+          <t>113282; 155790</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78860; 114379</t>
+          <t>79759; 114735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>110176; 142135</t>
+          <t>126132; 163167</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182952; 237947</t>
+          <t>183678; 238543</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189326; 244282</t>
+          <t>192856; 248618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146940; 195451</t>
+          <t>148749; 196342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>201834; 248184</t>
+          <t>231466; 283581</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171340</t>
+          <t>183471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>241446</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>412786</t>
+          <t>437648</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77449; 112981</t>
+          <t>78087; 113763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70371; 107476</t>
+          <t>69511; 106876</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100837; 142360</t>
+          <t>101996; 142940</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75003; 248306</t>
+          <t>160982; 209567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>134951; 175176</t>
+          <t>132536; 173727</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143133; 189428</t>
+          <t>144510; 191007</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131887; 175885</t>
+          <t>130581; 174308</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198776; 263356</t>
+          <t>234910; 274258</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223854; 278898</t>
+          <t>223595; 276677</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>225191; 284036</t>
+          <t>219892; 281633</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>243847; 306077</t>
+          <t>243211; 305538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>263019; 503249</t>
+          <t>407563; 469305</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219732</t>
+          <t>228651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>251831</t>
+          <t>279362</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>471563</t>
+          <t>508013</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>102858; 137575</t>
+          <t>101928; 137909</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95900; 133560</t>
+          <t>97254; 134890</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98534; 137602</t>
+          <t>99557; 137181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197532; 242652</t>
+          <t>204718; 250380</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136156; 175821</t>
+          <t>135163; 174076</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>184324; 230267</t>
+          <t>185819; 230070</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>180865; 228264</t>
+          <t>181156; 226510</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>234382; 269539</t>
+          <t>259583; 298129</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>248842; 302655</t>
+          <t>250038; 304898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>291049; 352237</t>
+          <t>292423; 351353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>290760; 352430</t>
+          <t>292125; 353187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>446595; 501309</t>
+          <t>480120; 536933</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131479</t>
+          <t>142202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>412730</t>
+          <t>228364</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>544209</t>
+          <t>370566</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>95376; 126398</t>
+          <t>94327; 125808</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>107292; 145413</t>
+          <t>105111; 142823</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91089; 126771</t>
+          <t>90402; 125348</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>117336; 146411</t>
+          <t>125667; 158041</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>170520; 203910</t>
+          <t>169505; 204993</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>192694; 228447</t>
+          <t>191747; 229882</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>183195; 223950</t>
+          <t>183594; 223602</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>307052; 533637</t>
+          <t>212440; 242691</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>273853; 324179</t>
+          <t>275069; 321682</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>308295; 358359</t>
+          <t>308804; 362075</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>286461; 337406</t>
+          <t>285372; 339961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>421506; 758663</t>
+          <t>348394; 393039</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>157195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>332555</t>
+          <t>360339</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>477656</t>
+          <t>517534</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113808; 141850</t>
+          <t>113949; 140524</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>132545; 166872</t>
+          <t>133462; 167675</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>125484; 153587</t>
+          <t>124374; 152688</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131315; 158817</t>
+          <t>143541; 171917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>208675; 245194</t>
+          <t>209097; 244498</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>283356; 317518</t>
+          <t>285242; 320206</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>252548; 293853</t>
+          <t>249872; 292898</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>320313; 343154</t>
+          <t>346476; 372667</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>330898; 376484</t>
+          <t>331238; 377332</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>428077; 475902</t>
+          <t>430674; 476676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>386618; 438320</t>
+          <t>387140; 437822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>458230; 495856</t>
+          <t>496369; 535820</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>554337; 643076</t>
+          <t>553244; 639974</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>597889; 692568</t>
+          <t>597213; 692784</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>583392; 675663</t>
+          <t>585906; 673772</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>670918; 946553</t>
+          <t>875133; 985944</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>933971; 1042379</t>
+          <t>938814; 1044684</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1059235; 1173836</t>
+          <t>1054956; 1165572</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>959073; 1071321</t>
+          <t>957490; 1065099</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1314973; 1891058</t>
+          <t>1331342; 1435380</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1510899; 1649700</t>
+          <t>1508456; 1648796</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1681452; 1828983</t>
+          <t>1686514; 1834573</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1576319; 1720911</t>
+          <t>1570059; 1711007</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2109545; 2774079</t>
+          <t>2244434; 2401930</t>
         </is>
       </c>
     </row>
